--- a/Project Cost/Project Cost.xlsx
+++ b/Project Cost/Project Cost.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\Project Cost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC27750A-0BAE-4BD6-9B64-4C91AA868EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4FD08-0602-4923-86F5-5B5BF6FC2A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Component Name</t>
   </si>
@@ -72,6 +72,27 @@
   </si>
   <si>
     <t>SIM800L GPRS GSM Module Core Board Quad-band TTL Serial Port with the antenna</t>
+  </si>
+  <si>
+    <t>ESP32 38pin</t>
+  </si>
+  <si>
+    <t>Capacitor 2200uf</t>
+  </si>
+  <si>
+    <t>Mini MP1584 DC-DC 3A Adjustable Buck Module</t>
+  </si>
+  <si>
+    <t>4 Channel IIC I2C Logic Level Bi-Directional Module Converter Module 5V to 3.3V</t>
+  </si>
+  <si>
+    <t>Solar Panel 12v 20w</t>
+  </si>
+  <si>
+    <t>SG Flash 20A Intelligent Battery Regulator for Panel LCD Display with USB 12V/24V PWM PWM Solar Charge Controller</t>
+  </si>
+  <si>
+    <t>12v lead acid battery</t>
   </si>
 </sst>
 </file>
@@ -132,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -143,6 +164,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -424,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -525,13 +549,13 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>76</v>
       </c>
       <c r="D7">
-        <v>76</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28" x14ac:dyDescent="0.35">
@@ -549,9 +573,107 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E9">
-        <f>SUM(D2:D8)</f>
-        <v>967</v>
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>500</v>
+      </c>
+      <c r="D9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>35</v>
+      </c>
+      <c r="D10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1500</v>
+      </c>
+      <c r="D13">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="42" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>500</v>
+      </c>
+      <c r="D14">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E16">
+        <f>SUM(D2:D15)</f>
+        <v>4682</v>
       </c>
     </row>
   </sheetData>
